--- a/SurveyQuestions/outputs/MECAMH_question_score.xlsx
+++ b/SurveyQuestions/outputs/MECAMH_question_score.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -58,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,18 +69,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/SurveyQuestions/outputs/MECAMH_question_score.xlsx
+++ b/SurveyQuestions/outputs/MECAMH_question_score.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -61,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -69,24 +66,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/SurveyQuestions/outputs/MECAMH_question_score.xlsx
+++ b/SurveyQuestions/outputs/MECAMH_question_score.xlsx
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>[State] Anxiety (modelled on the STAI)</t>
+          <t>Anxiety</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Anticipatory Traumatic Reaction – Feelings Sub-Scale (Hopwood et al. 2017)</t>
+          <t>Anticipatory Traumatic Reaction</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Coping Responses (Ojala 2012)</t>
+          <t>Coping Responses</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Climate Change Worry (Ojala 2012)</t>
+          <t>Climate Change Worry</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
